--- a/ds/planejamento/1semestre/planos/Planos_de_Ensino_SOP-temp.xlsx
+++ b/ds/planejamento/1semestre/planos/Planos_de_Ensino_SOP-temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESENVOLVIMENTO\Desktop\senai2026\ds\planejamento\1semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1567E67A-98C5-4593-9C66-CDB106C2CC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6613F49C-5352-4E1C-9527-C678882CA99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,70 +449,83 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1093,137 +1106,22 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1232,47 +1130,23 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1285,6 +1159,15 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1313,6 +1196,9 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1334,29 +1220,156 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1636,134 +1649,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="56" t="s">
+      <c r="B2" s="110"/>
+      <c r="C2" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="61" t="s">
+      <c r="D2" s="103"/>
+      <c r="E2" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="55" t="s">
+      <c r="F2" s="107"/>
+      <c r="G2" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55" t="s">
+      <c r="H2" s="87"/>
+      <c r="I2" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="63" t="s">
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="66" t="s">
+      <c r="F3" s="108"/>
+      <c r="G3" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="60" t="s">
+      <c r="B4" s="90"/>
+      <c r="C4" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="86"/>
+      <c r="E4" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="66" t="s">
+      <c r="F4" s="98"/>
+      <c r="G4" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="75" t="s">
+      <c r="A5" s="90"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="70" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="98" t="s">
+      <c r="D6" s="92"/>
+      <c r="E6" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="99"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
     </row>
     <row r="7" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1784,14 +1797,14 @@
       <c r="F9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72" t="s">
+      <c r="H9" s="94"/>
+      <c r="I9" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="72"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1829,14 +1842,14 @@
       <c r="F10" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="39" t="s">
+      <c r="H10" s="96"/>
+      <c r="I10" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="40"/>
+      <c r="J10" s="96"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1874,14 +1887,14 @@
       <c r="F11" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="40"/>
-      <c r="I11" s="37" t="s">
+      <c r="H11" s="96"/>
+      <c r="I11" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="38"/>
+      <c r="J11" s="88"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1919,14 +1932,14 @@
       <c r="F12" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="40"/>
-      <c r="I12" s="37" t="s">
+      <c r="H12" s="96"/>
+      <c r="I12" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="38"/>
+      <c r="J12" s="88"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1964,14 +1977,14 @@
       <c r="F13" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="37" t="s">
+      <c r="H13" s="96"/>
+      <c r="I13" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="38"/>
+      <c r="J13" s="88"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2009,14 +2022,14 @@
       <c r="F14" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="37" t="s">
+      <c r="H14" s="96"/>
+      <c r="I14" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="38"/>
+      <c r="J14" s="88"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2054,14 +2067,14 @@
       <c r="F15" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="37" t="s">
+      <c r="H15" s="96"/>
+      <c r="I15" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="J15" s="38"/>
+      <c r="J15" s="88"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -2099,14 +2112,14 @@
       <c r="F16" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="40"/>
-      <c r="I16" s="37" t="s">
+      <c r="H16" s="96"/>
+      <c r="I16" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="J16" s="38"/>
+      <c r="J16" s="88"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2144,14 +2157,14 @@
       <c r="F17" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="40"/>
-      <c r="I17" s="37" t="s">
+      <c r="H17" s="96"/>
+      <c r="I17" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="38"/>
+      <c r="J17" s="88"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -2189,14 +2202,14 @@
       <c r="F18" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="40"/>
-      <c r="I18" s="37" t="s">
+      <c r="H18" s="96"/>
+      <c r="I18" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="38"/>
+      <c r="J18" s="88"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -2234,14 +2247,14 @@
       <c r="F19" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="40"/>
-      <c r="I19" s="37" t="s">
+      <c r="H19" s="96"/>
+      <c r="I19" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="J19" s="38"/>
+      <c r="J19" s="88"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -2279,14 +2292,14 @@
       <c r="F20" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="115"/>
-      <c r="I20" s="116" t="s">
+      <c r="H20" s="68"/>
+      <c r="I20" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="J20" s="117"/>
+      <c r="J20" s="70"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -2317,10 +2330,10 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="121"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="74"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2340,18 +2353,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="127" t="s">
+      <c r="A22" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
-      <c r="J22" s="129"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2371,18 +2384,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2402,18 +2415,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="101"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2433,18 +2446,18 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="97" t="s">
+      <c r="A25" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2464,18 +2477,18 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="101"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="O26" s="1"/>
@@ -2491,18 +2504,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="97" t="s">
+      <c r="A27" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="97"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2522,18 +2535,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="101"/>
-      <c r="J28" s="101"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2553,18 +2566,18 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="122" t="s">
+      <c r="A29" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="122"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="122"/>
-      <c r="J29" s="122"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2584,22 +2597,22 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="123" t="s">
+      <c r="A30" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="124"/>
-      <c r="D30" s="125" t="s">
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="125"/>
-      <c r="F30" s="125"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="126"/>
-      <c r="I30" s="126"/>
-      <c r="J30" s="126"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2619,12 +2632,12 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="124"/>
-      <c r="B31" s="124"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="125"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
       <c r="G31" s="21">
         <v>1</v>
       </c>
@@ -2656,16 +2669,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="106" t="s">
+      <c r="A32" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="87"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="44"/>
       <c r="G32" s="7"/>
       <c r="H32" s="18"/>
       <c r="I32" s="19"/>
@@ -2689,12 +2702,12 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="107"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="44"/>
       <c r="G33" s="7"/>
       <c r="H33" s="18"/>
       <c r="I33" s="19"/>
@@ -2718,12 +2731,12 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="107"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="111"/>
+      <c r="A34" s="59"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63"/>
       <c r="G34" s="7"/>
       <c r="H34" s="18"/>
       <c r="I34" s="19"/>
@@ -2747,12 +2760,12 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="107"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="112"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="114"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="66"/>
       <c r="G35" s="7"/>
       <c r="H35" s="18"/>
       <c r="I35" s="19"/>
@@ -2776,12 +2789,12 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="109"/>
-      <c r="E36" s="110"/>
-      <c r="F36" s="111"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="63"/>
       <c r="G36" s="7"/>
       <c r="H36" s="18"/>
       <c r="I36" s="19"/>
@@ -2805,12 +2818,12 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="107"/>
-      <c r="B37" s="102"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="87"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
       <c r="G37" s="7"/>
       <c r="H37" s="18"/>
       <c r="I37" s="14"/>
@@ -2834,12 +2847,12 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="111"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="63"/>
       <c r="G38" s="7"/>
       <c r="H38" s="18"/>
       <c r="I38" s="14"/>
@@ -2863,14 +2876,14 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="83"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="93"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="127"/>
+      <c r="F39" s="128"/>
       <c r="G39" s="7"/>
       <c r="H39" s="18"/>
       <c r="I39" s="14"/>
@@ -2894,12 +2907,12 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="89"/>
-      <c r="B40" s="83"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="87"/>
+      <c r="A40" s="125"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
       <c r="G40" s="7"/>
       <c r="H40" s="18"/>
       <c r="I40" s="14"/>
@@ -2923,12 +2936,12 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="89"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="85"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="87"/>
+      <c r="A41" s="125"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
       <c r="G41" s="7"/>
       <c r="H41" s="18"/>
       <c r="I41" s="14"/>
@@ -2952,12 +2965,12 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="90"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="87"/>
+      <c r="A42" s="126"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
       <c r="G42" s="7"/>
       <c r="H42" s="18"/>
       <c r="I42" s="14"/>
@@ -2981,14 +2994,14 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="81"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="82"/>
+      <c r="A43" s="122"/>
+      <c r="B43" s="123"/>
+      <c r="C43" s="123"/>
+      <c r="D43" s="123"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="123"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="123"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3010,18 +3023,18 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="77" t="s">
+      <c r="A44" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="78"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="80" t="s">
+      <c r="B44" s="119"/>
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="78"/>
-      <c r="H44" s="79"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="120"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3046,17 +3059,17 @@
       <c r="A45" s="8">
         <v>8</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="45">
+      <c r="C45" s="78"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="77">
         <v>100</v>
       </c>
-      <c r="G45" s="43"/>
-      <c r="H45" s="44"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="79"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -3081,17 +3094,17 @@
       <c r="A46" s="8">
         <v>7</v>
       </c>
-      <c r="B46" s="94" t="s">
+      <c r="B46" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="95"/>
-      <c r="D46" s="95"/>
-      <c r="E46" s="96"/>
-      <c r="F46" s="45">
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="77">
         <v>95</v>
       </c>
-      <c r="G46" s="43"/>
-      <c r="H46" s="44"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="79"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3116,17 +3129,17 @@
       <c r="A47" s="8">
         <v>6</v>
       </c>
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="95"/>
-      <c r="D47" s="95"/>
-      <c r="E47" s="96"/>
-      <c r="F47" s="45">
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="82"/>
+      <c r="F47" s="77">
         <v>90</v>
       </c>
-      <c r="G47" s="43"/>
-      <c r="H47" s="44"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3151,17 +3164,17 @@
       <c r="A48" s="8">
         <v>5</v>
       </c>
-      <c r="B48" s="53" t="s">
+      <c r="B48" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="45">
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="77">
         <v>80</v>
       </c>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="79"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3186,17 +3199,17 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="53" t="s">
+      <c r="B49" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="45">
+      <c r="C49" s="78"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="77">
         <v>70</v>
       </c>
-      <c r="G49" s="43"/>
-      <c r="H49" s="44"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="79"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3221,17 +3234,17 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="53" t="s">
+      <c r="B50" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="45">
+      <c r="C50" s="78"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="77">
         <v>60</v>
       </c>
-      <c r="G50" s="43"/>
-      <c r="H50" s="44"/>
+      <c r="G50" s="78"/>
+      <c r="H50" s="79"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3256,17 +3269,17 @@
       <c r="A51" s="8">
         <v>2</v>
       </c>
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="45">
+      <c r="C51" s="78"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="77">
         <v>50</v>
       </c>
-      <c r="G51" s="43"/>
-      <c r="H51" s="44"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="79"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3291,17 +3304,17 @@
       <c r="A52" s="8">
         <v>1</v>
       </c>
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="45">
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="77">
         <v>30</v>
       </c>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="79"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3393,16 +3406,16 @@
       <c r="D55" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="47">
+      <c r="E55" s="111">
         <v>1</v>
       </c>
-      <c r="F55" s="47">
+      <c r="F55" s="111">
         <v>0</v>
       </c>
       <c r="G55" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="51" t="s">
+      <c r="H55" s="114" t="s">
         <v>43</v>
       </c>
       <c r="I55" s="1"/>
@@ -3432,10 +3445,10 @@
       <c r="D56" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="52"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="113"/>
+      <c r="H56" s="115"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -3457,18 +3470,18 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
+      <c r="B57" s="129"/>
+      <c r="C57" s="129"/>
+      <c r="D57" s="129"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="129"/>
+      <c r="G57" s="129"/>
+      <c r="H57" s="129"/>
+      <c r="I57" s="129"/>
+      <c r="J57" s="129"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -22049,57 +22062,19 @@
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:C31"/>
-    <mergeCell ref="D30:F31"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="A32:A38"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G5:J7"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="C2:D3"/>
@@ -22124,6 +22099,29 @@
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="F52:H52"/>
     <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G5:J7"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="F44:H44"/>
     <mergeCell ref="A43:H43"/>
@@ -22137,19 +22135,34 @@
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:C31"/>
+    <mergeCell ref="D30:F31"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A27:J27"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
